--- a/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
+++ b/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:37:07-05:00</t>
+    <t>2026-09-02T22:18:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
+++ b/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="599">
   <si>
     <t>Property</t>
   </si>
@@ -51,10 +51,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Maps ICD-10-CM diagnosis codes to CDSi observation codes used in immunization decision support.</t>
+    <t>Maps ICD-10-CM codes to CDSi observation codes used in immunization decision support. Generated from the cicada crosswalk.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -90,19 +93,25 @@
     <t>Source</t>
   </si>
   <si>
+    <t>http://fhirfli.dev/fhir/ig/cicada/ValueSet/vaccine-condition-codes-icd10</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>http://fhirfli.dev/fhir/ig/cicada/ValueSet/cdsi-observation-codes-vs</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/sid/icd-10-cm</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>https://www.cdc.gov/vaccines/programs/iis/cdsi</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Relationship</t>
+    <t>http://fhirfli.dev/fhir/ig/cicada/CodeSystem/cdsi-observation-codes</t>
   </si>
   <si>
     <t>D84.9</t>
@@ -111,7 +120,7 @@
     <t>Immunodeficiency, unspecified</t>
   </si>
   <si>
-    <t>source-is-narrower-than-target</t>
+    <t>equivalent</t>
   </si>
   <si>
     <t>003</t>
@@ -120,21 +129,108 @@
     <t>Immunocompromised</t>
   </si>
   <si>
+    <t>D83.9</t>
+  </si>
+  <si>
+    <t>Common variable immunodeficiency, unspecified</t>
+  </si>
+  <si>
+    <t>D80.9</t>
+  </si>
+  <si>
+    <t>Immunodeficiency with predominantly antibody defects, unspecified</t>
+  </si>
+  <si>
+    <t>D89.9</t>
+  </si>
+  <si>
+    <t>Disorder involving the immune mechanism, unspecified</t>
+  </si>
+  <si>
+    <t>D84.8</t>
+  </si>
+  <si>
+    <t>Other specified immunodeficiencies</t>
+  </si>
+  <si>
+    <t>Z94.84</t>
+  </si>
+  <si>
+    <t>Stem cells transplant status</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Recipient of a hematopoietic stem cell transplant</t>
+  </si>
+  <si>
+    <t>T86.00</t>
+  </si>
+  <si>
+    <t>Unspecified complication of bone marrow transplant</t>
+  </si>
+  <si>
+    <t>T86.09</t>
+  </si>
+  <si>
+    <t>Other complications of bone marrow transplant</t>
+  </si>
+  <si>
     <t>B18.2</t>
   </si>
   <si>
     <t>Chronic viral hepatitis C</t>
   </si>
   <si>
-    <t>equivalent</t>
-  </si>
-  <si>
     <t>005</t>
   </si>
   <si>
     <t>Hepatitis C virus infection</t>
   </si>
   <si>
+    <t>B17.10</t>
+  </si>
+  <si>
+    <t>Acute hepatitis C without hepatic coma</t>
+  </si>
+  <si>
+    <t>B17.11</t>
+  </si>
+  <si>
+    <t>Acute hepatitis C with hepatic coma</t>
+  </si>
+  <si>
+    <t>B19.20</t>
+  </si>
+  <si>
+    <t>Unspecified viral hepatitis C without hepatic coma</t>
+  </si>
+  <si>
+    <t>D66</t>
+  </si>
+  <si>
+    <t>Hereditary factor VIII deficiency</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>Receives clotting factor concentrates</t>
+  </si>
+  <si>
+    <t>D67</t>
+  </si>
+  <si>
+    <t>Hereditary factor IX deficiency</t>
+  </si>
+  <si>
+    <t>D68.2</t>
+  </si>
+  <si>
+    <t>Hereditary deficiency of other clotting factors</t>
+  </si>
+  <si>
     <t>Z33.1</t>
   </si>
   <si>
@@ -147,6 +243,96 @@
     <t>Pregnant</t>
   </si>
   <si>
+    <t>O09.90</t>
+  </si>
+  <si>
+    <t>Supervision of high risk pregnancy, unspecified, unspecified trimester</t>
+  </si>
+  <si>
+    <t>Z34.00</t>
+  </si>
+  <si>
+    <t>Encounter for supervision of normal first pregnancy, unspecified trimester</t>
+  </si>
+  <si>
+    <t>Z34.80</t>
+  </si>
+  <si>
+    <t>Encounter for supervision of other normal pregnancy, unspecified trimester</t>
+  </si>
+  <si>
+    <t>Z39.1</t>
+  </si>
+  <si>
+    <t>Encounter for care and examination of lactating mother</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Breastfeeding</t>
+  </si>
+  <si>
+    <t>G96.00</t>
+  </si>
+  <si>
+    <t>Cerebrospinal fluid leak, unspecified</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>Cerebrospinal fluid leaks</t>
+  </si>
+  <si>
+    <t>G96.01</t>
+  </si>
+  <si>
+    <t>Cranial cerebrospinal fluid leak, spontaneous</t>
+  </si>
+  <si>
+    <t>G96.02</t>
+  </si>
+  <si>
+    <t>Spinal cerebrospinal fluid leak, spontaneous</t>
+  </si>
+  <si>
+    <t>G96.08</t>
+  </si>
+  <si>
+    <t>Other cranial cerebrospinal fluid leak</t>
+  </si>
+  <si>
+    <t>G96.09</t>
+  </si>
+  <si>
+    <t>Other spinal cerebrospinal fluid leak</t>
+  </si>
+  <si>
+    <t>Z96.21</t>
+  </si>
+  <si>
+    <t>Cochlear implant status</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>Cochlear implants</t>
+  </si>
+  <si>
+    <t>Z83.2</t>
+  </si>
+  <si>
+    <t>Family history of diseases of the blood and blood-forming organs and certain disorders involving the immune mechanism</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>Family history of altered immunocompetence</t>
+  </si>
+  <si>
     <t>D81.9</t>
   </si>
   <si>
@@ -159,16 +345,124 @@
     <t>Severe Combined Immunodeficiency [SCID]</t>
   </si>
   <si>
+    <t>D81.0</t>
+  </si>
+  <si>
+    <t>Severe combined immunodeficiency [SCID] with reticular dysgenesis</t>
+  </si>
+  <si>
+    <t>D81.1</t>
+  </si>
+  <si>
+    <t>Severe combined immunodeficiency [SCID] with low T- and B-cell numbers</t>
+  </si>
+  <si>
+    <t>D81.2</t>
+  </si>
+  <si>
+    <t>Severe combined immunodeficiency [SCID] with low or normal B-cell numbers</t>
+  </si>
+  <si>
+    <t>D81.3</t>
+  </si>
+  <si>
+    <t>Adenosine deaminase [ADA] deficiency</t>
+  </si>
+  <si>
+    <t>D81.5</t>
+  </si>
+  <si>
+    <t>Purine nucleoside phosphorylase [PNP] deficiency</t>
+  </si>
+  <si>
+    <t>D81.6</t>
+  </si>
+  <si>
+    <t>Major histocompatibility complex class I deficiency</t>
+  </si>
+  <si>
+    <t>D81.7</t>
+  </si>
+  <si>
+    <t>Major histocompatibility complex class II deficiency</t>
+  </si>
+  <si>
+    <t>E10.9</t>
+  </si>
+  <si>
+    <t>Type 1 diabetes mellitus without complications</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
+  </si>
+  <si>
+    <t>E10.65</t>
+  </si>
+  <si>
+    <t>Type 1 diabetes mellitus with hyperglycemia</t>
+  </si>
+  <si>
     <t>E11.9</t>
   </si>
   <si>
     <t>Type 2 diabetes mellitus without complications</t>
   </si>
   <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>Diabetes</t>
+    <t>E11.65</t>
+  </si>
+  <si>
+    <t>Type 2 diabetes mellitus with hyperglycemia</t>
+  </si>
+  <si>
+    <t>E13.9</t>
+  </si>
+  <si>
+    <t>Other specified diabetes mellitus without complications</t>
+  </si>
+  <si>
+    <t>E08.9</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus due to underlying condition without complications</t>
+  </si>
+  <si>
+    <t>E09.9</t>
+  </si>
+  <si>
+    <t>Drug or chemical induced diabetes mellitus without complications</t>
+  </si>
+  <si>
+    <t>K70.30</t>
+  </si>
+  <si>
+    <t>Alcoholic cirrhosis of liver without ascites</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>Chronic liver disease</t>
+  </si>
+  <si>
+    <t>K70.31</t>
+  </si>
+  <si>
+    <t>Alcoholic cirrhosis of liver with ascites</t>
+  </si>
+  <si>
+    <t>K73.9</t>
+  </si>
+  <si>
+    <t>Chronic hepatitis, unspecified</t>
+  </si>
+  <si>
+    <t>K74.0</t>
+  </si>
+  <si>
+    <t>Hepatic fibrosis</t>
   </si>
   <si>
     <t>K74.60</t>
@@ -177,10 +471,40 @@
     <t>Unspecified cirrhosis of liver</t>
   </si>
   <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>Chronic liver disease</t>
+    <t>K74.69</t>
+  </si>
+  <si>
+    <t>Other cirrhosis of liver</t>
+  </si>
+  <si>
+    <t>K76.0</t>
+  </si>
+  <si>
+    <t>Fatty (change of) liver, not elsewhere classified</t>
+  </si>
+  <si>
+    <t>K76.9</t>
+  </si>
+  <si>
+    <t>Liver disease, unspecified</t>
+  </si>
+  <si>
+    <t>I25.10</t>
+  </si>
+  <si>
+    <t>Atherosclerotic heart disease of native coronary artery without angina pectoris</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>Chronic heart disease</t>
+  </si>
+  <si>
+    <t>I25.9</t>
+  </si>
+  <si>
+    <t>Chronic ischemic heart disease, unspecified</t>
   </si>
   <si>
     <t>I50.9</t>
@@ -189,10 +513,34 @@
     <t>Heart failure, unspecified</t>
   </si>
   <si>
-    <t>016</t>
-  </si>
-  <si>
-    <t>Chronic heart disease</t>
+    <t>I50.20</t>
+  </si>
+  <si>
+    <t>Unspecified systolic (congestive) heart failure</t>
+  </si>
+  <si>
+    <t>I50.30</t>
+  </si>
+  <si>
+    <t>Unspecified diastolic (congestive) heart failure</t>
+  </si>
+  <si>
+    <t>I42.9</t>
+  </si>
+  <si>
+    <t>Cardiomyopathy, unspecified</t>
+  </si>
+  <si>
+    <t>I42.0</t>
+  </si>
+  <si>
+    <t>Dilated cardiomyopathy</t>
+  </si>
+  <si>
+    <t>Q24.9</t>
+  </si>
+  <si>
+    <t>Congenital malformation of heart, unspecified</t>
   </si>
   <si>
     <t>J44.9</t>
@@ -207,6 +555,42 @@
     <t>Chronic lung disease</t>
   </si>
   <si>
+    <t>J44.1</t>
+  </si>
+  <si>
+    <t>Chronic obstructive pulmonary disease with (acute) exacerbation</t>
+  </si>
+  <si>
+    <t>J43.9</t>
+  </si>
+  <si>
+    <t>Emphysema, unspecified</t>
+  </si>
+  <si>
+    <t>J84.9</t>
+  </si>
+  <si>
+    <t>Interstitial pulmonary disease, unspecified</t>
+  </si>
+  <si>
+    <t>J84.10</t>
+  </si>
+  <si>
+    <t>Pulmonary fibrosis, unspecified</t>
+  </si>
+  <si>
+    <t>J47.9</t>
+  </si>
+  <si>
+    <t>Bronchiectasis, uncomplicated</t>
+  </si>
+  <si>
+    <t>P27.1</t>
+  </si>
+  <si>
+    <t>Bronchopulmonary dysplasia originating in the perinatal period</t>
+  </si>
+  <si>
     <t>D73.0</t>
   </si>
   <si>
@@ -216,7 +600,19 @@
     <t>018</t>
   </si>
   <si>
-    <t>Asplenia</t>
+    <t>Laboratory Evidence of Immunity or confirmation of Hepatitis A disease</t>
+  </si>
+  <si>
+    <t>Q89.01</t>
+  </si>
+  <si>
+    <t>Asplenia (congenital)</t>
+  </si>
+  <si>
+    <t>D73.89</t>
+  </si>
+  <si>
+    <t>Other diseases of spleen</t>
   </si>
   <si>
     <t>Z90.81</t>
@@ -225,16 +621,58 @@
     <t>Acquired absence of spleen</t>
   </si>
   <si>
+    <t>N18.1</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease, stage 1</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>Laboratory Evidence of Immunity or confirmation of Hepatitis B disease</t>
+  </si>
+  <si>
+    <t>N18.2</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease, stage 2 (mild)</t>
+  </si>
+  <si>
+    <t>N18.30</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease, stage 3 unspecified</t>
+  </si>
+  <si>
+    <t>N18.4</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease, stage 4 (severe)</t>
+  </si>
+  <si>
+    <t>N18.5</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease, stage 5</t>
+  </si>
+  <si>
     <t>N18.6</t>
   </si>
   <si>
     <t>End stage renal disease</t>
   </si>
   <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>Chronic renal failure</t>
+    <t>N18.9</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease, unspecified</t>
+  </si>
+  <si>
+    <t>Z99.2</t>
+  </si>
+  <si>
+    <t>Dependence on renal dialysis</t>
   </si>
   <si>
     <t>B20</t>
@@ -246,7 +684,7 @@
     <t>026</t>
   </si>
   <si>
-    <t>HIV/AIDS - immunocompromised</t>
+    <t>Persons with perinatal HIV infection who do not have evidence of severe immunosuppression and who were vaccinated with MMR before establishment of antiviral therapy [ART]</t>
   </si>
   <si>
     <t>Z21</t>
@@ -255,16 +693,46 @@
     <t>Asymptomatic human immunodeficiency virus [HIV] infection status</t>
   </si>
   <si>
+    <t>J45.20</t>
+  </si>
+  <si>
+    <t>Mild intermittent asthma, uncomplicated</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>Asthma</t>
+  </si>
+  <si>
+    <t>J45.30</t>
+  </si>
+  <si>
+    <t>Mild persistent asthma, uncomplicated</t>
+  </si>
+  <si>
+    <t>J45.40</t>
+  </si>
+  <si>
+    <t>Moderate persistent asthma, uncomplicated</t>
+  </si>
+  <si>
+    <t>J45.50</t>
+  </si>
+  <si>
+    <t>Severe persistent asthma, uncomplicated</t>
+  </si>
+  <si>
     <t>J45.909</t>
   </si>
   <si>
     <t>Unspecified asthma, uncomplicated</t>
   </si>
   <si>
-    <t>027</t>
-  </si>
-  <si>
-    <t>Asthma</t>
+    <t>J45.998</t>
+  </si>
+  <si>
+    <t>Other asthma</t>
   </si>
   <si>
     <t>K56.1</t>
@@ -276,6 +744,48 @@
     <t>028</t>
   </si>
   <si>
+    <t>K52.9</t>
+  </si>
+  <si>
+    <t>Noninfective gastroenteritis and colitis, unspecified</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Acute gastroenteritis</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>Infectious gastroenteritis and colitis, unspecified</t>
+  </si>
+  <si>
+    <t>A08.0</t>
+  </si>
+  <si>
+    <t>Rotaviral enteritis</t>
+  </si>
+  <si>
+    <t>A08.39</t>
+  </si>
+  <si>
+    <t>Other viral enteritis</t>
+  </si>
+  <si>
+    <t>R50.9</t>
+  </si>
+  <si>
+    <t>Fever, unspecified</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>Acute febrile illness</t>
+  </si>
+  <si>
     <t>A15.0</t>
   </si>
   <si>
@@ -288,6 +798,36 @@
     <t>Tuberculosis</t>
   </si>
   <si>
+    <t>A15.9</t>
+  </si>
+  <si>
+    <t>Respiratory tuberculosis unspecified</t>
+  </si>
+  <si>
+    <t>A18.89</t>
+  </si>
+  <si>
+    <t>Tuberculosis of other sites</t>
+  </si>
+  <si>
+    <t>A19.9</t>
+  </si>
+  <si>
+    <t>Miliary tuberculosis, unspecified</t>
+  </si>
+  <si>
+    <t>R76.11</t>
+  </si>
+  <si>
+    <t>Nonspecific reaction to tuberculin skin test without active tuberculosis</t>
+  </si>
+  <si>
+    <t>Z86.11</t>
+  </si>
+  <si>
+    <t>Personal history of tuberculosis</t>
+  </si>
+  <si>
     <t>Z79.82</t>
   </si>
   <si>
@@ -298,6 +838,978 @@
   </si>
   <si>
     <t>Receiving long-term aspirin therapy</t>
+  </si>
+  <si>
+    <t>Z11.3</t>
+  </si>
+  <si>
+    <t>Encounter for screening for infections with a predominantly sexual mode of transmission</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>Receives treatment for STD</t>
+  </si>
+  <si>
+    <t>Z11.4</t>
+  </si>
+  <si>
+    <t>Encounter for screening for human immunodeficiency virus [HIV]</t>
+  </si>
+  <si>
+    <t>Z20.2</t>
+  </si>
+  <si>
+    <t>Contact with and (suspected) exposure to infections with a predominantly sexual mode of transmission</t>
+  </si>
+  <si>
+    <t>F19.10</t>
+  </si>
+  <si>
+    <t>Other psychoactive substance abuse, uncomplicated</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>Illicit drug use</t>
+  </si>
+  <si>
+    <t>F14.10</t>
+  </si>
+  <si>
+    <t>Cocaine abuse, uncomplicated</t>
+  </si>
+  <si>
+    <t>F11.10</t>
+  </si>
+  <si>
+    <t>Opioid abuse, uncomplicated</t>
+  </si>
+  <si>
+    <t>F16.10</t>
+  </si>
+  <si>
+    <t>Hallucinogen abuse, uncomplicated</t>
+  </si>
+  <si>
+    <t>F17.210</t>
+  </si>
+  <si>
+    <t>Nicotine dependence, cigarettes, uncomplicated</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>Smoke cigarettes</t>
+  </si>
+  <si>
+    <t>Z72.0</t>
+  </si>
+  <si>
+    <t>Tobacco use</t>
+  </si>
+  <si>
+    <t>F10.20</t>
+  </si>
+  <si>
+    <t>Alcohol dependence, uncomplicated</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>Alcoholism</t>
+  </si>
+  <si>
+    <t>F10.10</t>
+  </si>
+  <si>
+    <t>Alcohol abuse, uncomplicated</t>
+  </si>
+  <si>
+    <t>Z11.59</t>
+  </si>
+  <si>
+    <t>Encounter for screening for other viral diseases</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>Household contact with hepatitis B surface antigen-positive persons</t>
+  </si>
+  <si>
+    <t>G31.9</t>
+  </si>
+  <si>
+    <t>Degenerative disease of nervous system, unspecified</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>Progressive neurologic disorder</t>
+  </si>
+  <si>
+    <t>T50.B95A</t>
+  </si>
+  <si>
+    <t>Adverse effect of other viral vaccines, initial encounter</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>Received inactivated or unknown measles vaccine between 1963-1967</t>
+  </si>
+  <si>
+    <t>Z88.9</t>
+  </si>
+  <si>
+    <t>Allergy status to unspecified drugs, medicaments and biological substances</t>
+  </si>
+  <si>
+    <t>Z91.012</t>
+  </si>
+  <si>
+    <t>Allergy to eggs</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Polio</t>
+  </si>
+  <si>
+    <t>T50.A15A</t>
+  </si>
+  <si>
+    <t>Adverse effect of pertussis vaccine, including combinations with a pertussis component, initial encounter</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Pertussis</t>
+  </si>
+  <si>
+    <t>T50.A95A</t>
+  </si>
+  <si>
+    <t>Adverse effect of other bacterial vaccines, initial encounter</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Diphtheria</t>
+  </si>
+  <si>
+    <t>T78.1</t>
+  </si>
+  <si>
+    <t>Other adverse food reactions, not elsewhere classified</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Allergic reaction to egg protein</t>
+  </si>
+  <si>
+    <t>Z91.018</t>
+  </si>
+  <si>
+    <t>Allergy to other foods</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to gelatin</t>
+  </si>
+  <si>
+    <t>T78.40XA</t>
+  </si>
+  <si>
+    <t>Allergy, unspecified, initial encounter</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to arginine</t>
+  </si>
+  <si>
+    <t>Z91.040</t>
+  </si>
+  <si>
+    <t>Latex allergy status</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Allergic reaction to latex</t>
+  </si>
+  <si>
+    <t>Z88.1</t>
+  </si>
+  <si>
+    <t>Allergy status to other antibiotic agents</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to gentamicin</t>
+  </si>
+  <si>
+    <t>T36.5X5A</t>
+  </si>
+  <si>
+    <t>Adverse effect of aminoglycosides, initial encounter</t>
+  </si>
+  <si>
+    <t>T36.8X5A</t>
+  </si>
+  <si>
+    <t>Adverse effect of other systemic antibiotics, initial encounter</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to polymyxin B</t>
+  </si>
+  <si>
+    <t>T78.49XA</t>
+  </si>
+  <si>
+    <t>Other allergy, initial encounter</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>Hypersensitivity to the preservative 2-phenoxyethanol</t>
+  </si>
+  <si>
+    <t>T45.7X5A</t>
+  </si>
+  <si>
+    <t>Adverse effect of anticoagulant antagonists, vitamin K and other coagulants, initial encounter</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to protamine sulfate</t>
+  </si>
+  <si>
+    <t>Z88.8</t>
+  </si>
+  <si>
+    <t>Allergy status to other drugs, medicaments and biological substances</t>
+  </si>
+  <si>
+    <t>Z59.00</t>
+  </si>
+  <si>
+    <t>Homelessness unspecified</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Homelessness</t>
+  </si>
+  <si>
+    <t>D84.821</t>
+  </si>
+  <si>
+    <t>Immunodeficiency due to drugs</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Travel to or working in countries that have high or intermediate endemicity of Hepatitis A</t>
+  </si>
+  <si>
+    <t>C80.0</t>
+  </si>
+  <si>
+    <t>Disseminated malignant neoplasm, unspecified</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Generalized malignant neoplasm</t>
+  </si>
+  <si>
+    <t>C80.1</t>
+  </si>
+  <si>
+    <t>Malignant (primary) neoplasm, unspecified</t>
+  </si>
+  <si>
+    <t>Z94.0</t>
+  </si>
+  <si>
+    <t>Kidney transplant status</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Solid organ transplantation</t>
+  </si>
+  <si>
+    <t>Z94.1</t>
+  </si>
+  <si>
+    <t>Heart transplant status</t>
+  </si>
+  <si>
+    <t>Z94.2</t>
+  </si>
+  <si>
+    <t>Lung transplant status</t>
+  </si>
+  <si>
+    <t>Z94.4</t>
+  </si>
+  <si>
+    <t>Liver transplant status</t>
+  </si>
+  <si>
+    <t>Z94.9</t>
+  </si>
+  <si>
+    <t>Transplanted organ and tissue status, unspecified</t>
+  </si>
+  <si>
+    <t>Z79.52</t>
+  </si>
+  <si>
+    <t>Long term (current) use of systemic steroids</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>Immunosuppressive therapy</t>
+  </si>
+  <si>
+    <t>Z79.899</t>
+  </si>
+  <si>
+    <t>Other long term (current) drug therapy</t>
+  </si>
+  <si>
+    <t>Z51.0</t>
+  </si>
+  <si>
+    <t>Encounter for antineoplastic radiation therapy</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Radiation therapy</t>
+  </si>
+  <si>
+    <t>N18.3</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease, stage 3 (moderate)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease</t>
+  </si>
+  <si>
+    <t>N04.9</t>
+  </si>
+  <si>
+    <t>Nephrotic syndrome with unspecified morphologic changes</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Travel to areas at risk for Yellow Fever transmission</t>
+  </si>
+  <si>
+    <t>Z51.11</t>
+  </si>
+  <si>
+    <t>Encounter for antineoplastic chemotherapy</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Chemotherapy</t>
+  </si>
+  <si>
+    <t>Z51.12</t>
+  </si>
+  <si>
+    <t>Encounter for antineoplastic immunotherapy</t>
+  </si>
+  <si>
+    <t>Z04.81</t>
+  </si>
+  <si>
+    <t>Encounter for examination and observation of victim following forced sexual exploitation</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>History of sexual abuse or assault</t>
+  </si>
+  <si>
+    <t>T74.21XA</t>
+  </si>
+  <si>
+    <t>Adult sexual abuse, confirmed, initial encounter</t>
+  </si>
+  <si>
+    <t>T74.22XA</t>
+  </si>
+  <si>
+    <t>Child sexual abuse, confirmed, initial encounter</t>
+  </si>
+  <si>
+    <t>Z34.90</t>
+  </si>
+  <si>
+    <t>Encounter for supervision of normal pregnancy, unspecified, unspecified trimester</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Onset of pregnancy</t>
+  </si>
+  <si>
+    <t>C95.90</t>
+  </si>
+  <si>
+    <t>Leukemia, unspecified not having achieved remission</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Leukemia</t>
+  </si>
+  <si>
+    <t>C91.00</t>
+  </si>
+  <si>
+    <t>Acute lymphoblastic leukemia not having achieved remission</t>
+  </si>
+  <si>
+    <t>C92.00</t>
+  </si>
+  <si>
+    <t>Acute myeloblastic leukemia, not having achieved remission</t>
+  </si>
+  <si>
+    <t>C85.90</t>
+  </si>
+  <si>
+    <t>Non-Hodgkin lymphoma, unspecified, unspecified site</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Lymphoma</t>
+  </si>
+  <si>
+    <t>C84.40</t>
+  </si>
+  <si>
+    <t>Peripheral T-cell lymphoma, not elsewhere classified, unspecified site</t>
+  </si>
+  <si>
+    <t>C81.90</t>
+  </si>
+  <si>
+    <t>Hodgkin lymphoma, unspecified, unspecified site</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Hodgkin's disease</t>
+  </si>
+  <si>
+    <t>C90.00</t>
+  </si>
+  <si>
+    <t>Multiple myeloma not having achieved remission</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Multiple myeloma</t>
+  </si>
+  <si>
+    <t>C96.9</t>
+  </si>
+  <si>
+    <t>Malignant neoplasm of lymphoid, hematopoietic and related tissue, unspecified</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Active treatment for hematologic malignancies</t>
+  </si>
+  <si>
+    <t>Z59.3</t>
+  </si>
+  <si>
+    <t>Problems related to living in residential institution</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of any egg-based IIV or LAIV influenza vaccine</t>
+  </si>
+  <si>
+    <t>J84.89</t>
+  </si>
+  <si>
+    <t>Other specified interstitial pulmonary diseases</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Interstitial lung disease</t>
+  </si>
+  <si>
+    <t>E84.0</t>
+  </si>
+  <si>
+    <t>Cystic fibrosis with pulmonary manifestations</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Cystic fibrosis</t>
+  </si>
+  <si>
+    <t>E84.9</t>
+  </si>
+  <si>
+    <t>Cystic fibrosis, unspecified</t>
+  </si>
+  <si>
+    <t>I27.0</t>
+  </si>
+  <si>
+    <t>Primary pulmonary hypertension</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Pulmonary hypertension</t>
+  </si>
+  <si>
+    <t>I27.20</t>
+  </si>
+  <si>
+    <t>Pulmonary hypertension, unspecified</t>
+  </si>
+  <si>
+    <t>I27.9</t>
+  </si>
+  <si>
+    <t>Pulmonary heart disease, unspecified</t>
+  </si>
+  <si>
+    <t>F03.90</t>
+  </si>
+  <si>
+    <t>Unspecified dementia, unspecified severity, without behavioral disturbance, psychotic disturbance, mood disturbance, and anxiety</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Dementia</t>
+  </si>
+  <si>
+    <t>G30.9</t>
+  </si>
+  <si>
+    <t>Alzheimer's disease, unspecified</t>
+  </si>
+  <si>
+    <t>Q90.9</t>
+  </si>
+  <si>
+    <t>Down syndrome, unspecified</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>Down syndrome</t>
+  </si>
+  <si>
+    <t>E66.9</t>
+  </si>
+  <si>
+    <t>Obesity, unspecified</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>Obesity</t>
+  </si>
+  <si>
+    <t>E66.01</t>
+  </si>
+  <si>
+    <t>Morbid (severe) obesity due to excess calories</t>
+  </si>
+  <si>
+    <t>D56.9</t>
+  </si>
+  <si>
+    <t>Thalassemia, unspecified</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Thalassemia</t>
+  </si>
+  <si>
+    <t>D56.0</t>
+  </si>
+  <si>
+    <t>Alpha thalassemia</t>
+  </si>
+  <si>
+    <t>D56.1</t>
+  </si>
+  <si>
+    <t>Beta thalassemia</t>
+  </si>
+  <si>
+    <t>I67.9</t>
+  </si>
+  <si>
+    <t>Cerebrovascular disease, unspecified</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>Cerebrovascular disease</t>
+  </si>
+  <si>
+    <t>I63.9</t>
+  </si>
+  <si>
+    <t>Cerebral infarction, unspecified</t>
+  </si>
+  <si>
+    <t>F19.20</t>
+  </si>
+  <si>
+    <t>Other psychoactive substance dependence, uncomplicated</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Substance use disorder</t>
+  </si>
+  <si>
+    <t>F99</t>
+  </si>
+  <si>
+    <t>Mental disorder, not otherwise specified</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>Mental Health conditions</t>
+  </si>
+  <si>
+    <t>L20.9</t>
+  </si>
+  <si>
+    <t>Atopic dermatitis, unspecified</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of orthopoxvirus vaccine</t>
+  </si>
+  <si>
+    <t>L20.89</t>
+  </si>
+  <si>
+    <t>Other atopic dermatitis</t>
+  </si>
+  <si>
+    <t>L26</t>
+  </si>
+  <si>
+    <t>Exfoliative dermatitis</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Household contact with history or presence of atopic dermatitis</t>
+  </si>
+  <si>
+    <t>L10.9</t>
+  </si>
+  <si>
+    <t>Pemphigus, unspecified</t>
+  </si>
+  <si>
+    <t>Z20.828</t>
+  </si>
+  <si>
+    <t>Contact with and (suspected) exposure to other viral communicable diseases</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>Healthcare personnel who care for patients infected with less virulent orthopoxviruses (e.g., Vaccinia virus or Cowpox virus)</t>
+  </si>
+  <si>
+    <t>I51.9</t>
+  </si>
+  <si>
+    <t>Heart disease, unspecified</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>Chronic cardiovascular disease</t>
+  </si>
+  <si>
+    <t>E66.2</t>
+  </si>
+  <si>
+    <t>Morbid (severe) obesity with alveolar hypoventilation</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus complicated by chronic kidney disease</t>
+  </si>
+  <si>
+    <t>D75.9</t>
+  </si>
+  <si>
+    <t>Disease of blood and blood-forming organs, unspecified</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Chronic hematologic disorders</t>
+  </si>
+  <si>
+    <t>D57.1</t>
+  </si>
+  <si>
+    <t>Sickle-cell disease without crisis</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Sickle cell disease</t>
+  </si>
+  <si>
+    <t>D57.00</t>
+  </si>
+  <si>
+    <t>Hb-SS disease with crisis, unspecified</t>
+  </si>
+  <si>
+    <t>R54</t>
+  </si>
+  <si>
+    <t>Age-related physical debility</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Frailty</t>
+  </si>
+  <si>
+    <t>E11.40</t>
+  </si>
+  <si>
+    <t>Type 2 diabetes mellitus with diabetic neuropathy, unspecified</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus complicated by neuropathy</t>
+  </si>
+  <si>
+    <t>E10.40</t>
+  </si>
+  <si>
+    <t>Type 1 diabetes mellitus with diabetic neuropathy, unspecified</t>
+  </si>
+  <si>
+    <t>E13.40</t>
+  </si>
+  <si>
+    <t>Other specified diabetes mellitus with diabetic neuropathy, unspecified</t>
+  </si>
+  <si>
+    <t>E11.319</t>
+  </si>
+  <si>
+    <t>Type 2 diabetes mellitus with unspecified diabetic retinopathy without macular edema</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus complicated by retinopathy</t>
+  </si>
+  <si>
+    <t>E10.319</t>
+  </si>
+  <si>
+    <t>Type 1 diabetes mellitus with unspecified diabetic retinopathy without macular edema</t>
+  </si>
+  <si>
+    <t>E11.69</t>
+  </si>
+  <si>
+    <t>Type 2 diabetes mellitus with other specified complication</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus complicated by end-organ damage</t>
+  </si>
+  <si>
+    <t>E10.69</t>
+  </si>
+  <si>
+    <t>Type 1 diabetes mellitus with other specified complication</t>
+  </si>
+  <si>
+    <t>E13.69</t>
+  </si>
+  <si>
+    <t>Other specified diabetes mellitus with other specified complication</t>
+  </si>
+  <si>
+    <t>Z79.4</t>
+  </si>
+  <si>
+    <t>Long term (current) use of insulin</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Diabetes requiring treatment with insulin</t>
+  </si>
+  <si>
+    <t>Z94.83</t>
+  </si>
+  <si>
+    <t>Pancreas transplant status</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Diabetes requiring treatment with sodium-glucose cotransporter-2 (SGLT2) inhibitor</t>
+  </si>
+  <si>
+    <t>D80.1</t>
+  </si>
+  <si>
+    <t>Nonfamilial hypogammaglobulinemia</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Chikungunya vaccine</t>
+  </si>
+  <si>
+    <t>D80.0</t>
+  </si>
+  <si>
+    <t>Hereditary hypogammaglobulinemia</t>
+  </si>
+  <si>
+    <t>D84.1</t>
+  </si>
+  <si>
+    <t>Defects in the complement system</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Early component complement inhibitor use</t>
+  </si>
+  <si>
+    <t>D58.2</t>
+  </si>
+  <si>
+    <t>Other hemoglobinopathies</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Laboratory worker with potential for exposure to chikungunya virus</t>
+  </si>
+  <si>
+    <t>D57.3</t>
+  </si>
+  <si>
+    <t>Sickle-cell trait</t>
   </si>
 </sst>
 </file>
@@ -488,74 +2000,76 @@
       <c r="A7" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -565,75 +2079,75 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>29</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="C4" t="s" s="2">
+      <c r="E4" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -644,251 +2158,3345 @@
         <v>41</v>
       </c>
       <c r="C5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>73</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>85</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="B19" t="s" s="2">
+      <c r="C24" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="C19" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s" s="2">
+      <c r="B25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="E19" t="s" s="2">
+      <c r="C25" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
         <v>94</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D64" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D67" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D72" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D73" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D74" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D75" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D76" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D80" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D82" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D84" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D85" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E85" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D86" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E86" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D87" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D88" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="E88" t="s" s="2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D89" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="E89" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D90" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="E90" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D91" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="E91" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="E92" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="E93" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="E94" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="E95" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="E97" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="E98" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="E99" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="E100" t="s" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D101" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="E101" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="E104" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="E106" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="E107" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D108" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="E108" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="E109" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="E110" t="s" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="E111" t="s" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="E112" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E113" t="s" s="2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D114" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="E114" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="E115" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="E116" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="E120" t="s" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="E121" t="s" s="2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D122" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="E122" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D123" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="E123" t="s" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D124" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="E124" t="s" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D125" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="E125" t="s" s="2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D126" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="E126" t="s" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D127" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="E127" t="s" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D128" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="E128" t="s" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D129" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="E129" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D130" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="E130" t="s" s="2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D131" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="E131" t="s" s="2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="E132" t="s" s="2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="E133" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="E134" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D135" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="E135" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D136" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="E136" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D137" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="E137" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D138" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="E138" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D139" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="E139" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D140" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="E140" t="s" s="2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D141" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="E141" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D142" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="E142" t="s" s="2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D143" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="E143" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D144" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="E144" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D145" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="E145" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D146" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="E146" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D147" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="E147" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C148" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D148" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="E148" t="s" s="2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C149" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D149" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="E149" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D150" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="E150" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C151" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D151" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="E151" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D152" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="E152" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C153" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D153" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="E153" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D154" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E154" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C155" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D155" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="E155" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D156" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="E156" t="s" s="2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D157" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="E157" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D158" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="E158" t="s" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C159" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D159" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="E159" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D160" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="E160" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D161" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E161" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D162" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E162" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C163" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D163" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E163" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D164" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="E164" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D165" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="E165" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D166" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="E166" t="s" s="2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D167" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="E167" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C168" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D168" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="E168" t="s" s="2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D169" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="E169" t="s" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D170" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="E170" t="s" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D171" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="E171" t="s" s="2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D172" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="E172" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D173" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="E173" t="s" s="2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D174" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="E174" t="s" s="2">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C175" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D175" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="E175" t="s" s="2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D176" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="E176" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D177" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="E177" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D178" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="E178" t="s" s="2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D179" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="E179" t="s" s="2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D180" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="E180" t="s" s="2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D181" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="E181" t="s" s="2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D182" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="E182" t="s" s="2">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D183" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="E183" t="s" s="2">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D184" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="E184" t="s" s="2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D185" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="E185" t="s" s="2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D186" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="E186" t="s" s="2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D187" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="E187" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C188" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D188" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="E188" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C189" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D189" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="E189" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D190" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="E190" t="s" s="2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D191" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="E191" t="s" s="2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D192" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="E192" t="s" s="2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C193" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D193" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="E193" t="s" s="2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C194" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D194" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="E194" t="s" s="2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D195" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="E195" t="s" s="2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D196" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="E196" t="s" s="2">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C197" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D197" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="E197" t="s" s="2">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D198" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="E198" t="s" s="2">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D199" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="E199" t="s" s="2">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D200" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="E200" t="s" s="2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="E201" t="s" s="2">
+        <v>596</v>
       </c>
     </row>
   </sheetData>

--- a/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
+++ b/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
+++ b/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T23:13:14-04:00</t>
+    <t>2026-09-07T18:40:23-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
+++ b/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="600">
   <si>
     <t>Property</t>
   </si>
@@ -36,6 +36,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Icd10ToCdsiObservation</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:40:23-04:00</t>
+    <t>2026-09-07T19:28:06-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1978,98 +1981,100 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2084,3419 +2089,3419 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>30</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E24" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E31" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D31" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="E39" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E46" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>143</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="E54" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="E54" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E62" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D62" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="E62" t="s" s="2">
-        <v>179</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="E69" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D69" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="E69" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D73" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="E73" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D73" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="E73" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="E81" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="E83" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>229</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D88" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="E88" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="E88" t="s" s="2">
-        <v>241</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D90" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="E90" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D90" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="E90" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="E95" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D95" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="E95" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="E102" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D102" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="E102" t="s" s="2">
-        <v>278</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="E105" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D105" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="E105" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="E109" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D109" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="E109" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="E111" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D111" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="E111" t="s" s="2">
-        <v>302</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="E115" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D115" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="E115" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D124" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="E124" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D124" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="E124" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D128" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="E128" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D128" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="E128" t="s" s="2">
-        <v>364</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="E132" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D132" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="E132" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="E134" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D134" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="E134" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D135" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D139" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="E139" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D139" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="E139" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E141" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D144" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="E144" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D144" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="E144" t="s" s="2">
-        <v>414</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D145" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D146" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="E146" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C146" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D146" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="E146" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D147" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E147" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D148" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D150" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="E150" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D150" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="E150" t="s" s="2">
-        <v>432</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D152" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C153" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D153" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="E153" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C153" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D153" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="E153" t="s" s="2">
-        <v>440</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D154" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D158" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D160" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="E160" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D160" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="E160" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D161" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E161" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D162" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="E162" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D162" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="E162" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D165" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="E165" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D165" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="E165" t="s" s="2">
-        <v>480</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D167" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C168" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D168" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="E168" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C168" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D168" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="E168" t="s" s="2">
-        <v>490</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D169" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E169" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D170" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="E170" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C170" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D170" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="E170" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D171" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D172" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D173" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="E173" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="C173" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D173" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="E173" t="s" s="2">
-        <v>504</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E175" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D177" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="E177" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C177" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D177" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="E177" t="s" s="2">
-        <v>518</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D179" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="E179" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D179" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="E179" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D180" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D185" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="E185" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C185" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D185" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="E185" t="s" s="2">
-        <v>546</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D186" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C188" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D188" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="E188" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C188" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D188" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="E188" t="s" s="2">
-        <v>556</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D190" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D191" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E191" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C191" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D191" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="E191" t="s" s="2">
-        <v>564</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D192" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E192" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C193" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D193" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="E193" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C193" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D193" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="E193" t="s" s="2">
-        <v>570</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E194" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D195" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E195" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D196" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E196" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D197" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E197" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D198" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="E198" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C198" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D198" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="E198" t="s" s="2">
-        <v>586</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D199" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E199" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E200" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="E201" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C201" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D201" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="E201" t="s" s="2">
-        <v>596</v>
       </c>
     </row>
   </sheetData>

--- a/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
+++ b/jaspr/web/cicada_ig/Icd10ToCdsiObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T19:28:06-04:00</t>
+    <t>2026-09-07T19:51:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
